--- a/artfynd/A 62829-2025 artfynd.xlsx
+++ b/artfynd/A 62829-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131041815</v>
+        <v>131039759</v>
       </c>
       <c r="B2" t="n">
-        <v>79249</v>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tandbergsvasseln, Dlr</t>
+          <t>Gotvad, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479077</v>
+        <v>479059</v>
       </c>
       <c r="R2" t="n">
-        <v>6791829</v>
+        <v>6792254</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,11 +756,6 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,14 +782,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131041641</v>
+        <v>131038578</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -818,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tandbergsvasseln, Dlr</t>
+          <t>Gotvad, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479078</v>
+        <v>479079</v>
       </c>
       <c r="R3" t="n">
-        <v>6791615</v>
+        <v>6792781</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,11 +863,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131039759</v>
+        <v>131038654</v>
       </c>
       <c r="B4" t="n">
-        <v>91838</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479059</v>
+        <v>479094</v>
       </c>
       <c r="R4" t="n">
-        <v>6792254</v>
+        <v>6792753</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,14 +996,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131040375</v>
+        <v>131038772</v>
       </c>
       <c r="B5" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1041,13 +1031,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479088</v>
+        <v>479121</v>
       </c>
       <c r="R5" t="n">
-        <v>6792211</v>
+        <v>6792727</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1087,6 +1077,11 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,53 +1108,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131042212</v>
+        <v>131039119</v>
       </c>
       <c r="B6" t="n">
-        <v>57076</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gotvad, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479114</v>
+        <v>479105</v>
       </c>
       <c r="R6" t="n">
-        <v>6792438</v>
+        <v>6792638</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,14 +1215,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131042226</v>
+        <v>131039391</v>
       </c>
       <c r="B7" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1260,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479114</v>
+        <v>479092</v>
       </c>
       <c r="R7" t="n">
-        <v>6792438</v>
+        <v>6792603</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1295,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,12 +1295,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter,synfältet</t>
+          <t>Miljöbilder. Rikligt till måttligt i en radie av ca 50 meter,  synfältet</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,50 +1327,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131038653</v>
+        <v>131039488</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gotvad, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479094</v>
+        <v>479104</v>
       </c>
       <c r="R8" t="n">
-        <v>6792753</v>
+        <v>6792550</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,6 +1408,11 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,32 +1439,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131040374</v>
+        <v>131039523</v>
       </c>
       <c r="B9" t="n">
-        <v>79007</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1484,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479088</v>
+        <v>479079</v>
       </c>
       <c r="R9" t="n">
-        <v>6792211</v>
+        <v>6792517</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,14 +1546,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131039523</v>
+        <v>131039579</v>
       </c>
       <c r="B10" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1594,10 +1584,10 @@
         <v>479079</v>
       </c>
       <c r="R10" t="n">
-        <v>6792517</v>
+        <v>6792475</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1637,6 +1627,11 @@
       <c r="AB10" t="inlineStr">
         <is>
           <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,14 +1658,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131041972</v>
+        <v>131039672</v>
       </c>
       <c r="B11" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1694,17 +1689,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tandbergsvasseln, Dlr</t>
+          <t>Gotvad, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479096</v>
+        <v>479066</v>
       </c>
       <c r="R11" t="n">
-        <v>6792085</v>
+        <v>6792326</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1775,14 +1770,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131039119</v>
+        <v>131039763</v>
       </c>
       <c r="B12" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1810,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479105</v>
+        <v>479059</v>
       </c>
       <c r="R12" t="n">
-        <v>6792638</v>
+        <v>6792254</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1882,32 +1877,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131040483</v>
+        <v>131040375</v>
       </c>
       <c r="B13" t="n">
-        <v>78652</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1989,53 +1984,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131039519</v>
+        <v>131040448</v>
       </c>
       <c r="B14" t="n">
-        <v>8451</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gotvad, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>479079</v>
+        <v>479100</v>
       </c>
       <c r="R14" t="n">
-        <v>6792517</v>
+        <v>6792209</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2075,6 +2065,11 @@
       <c r="AB14" t="inlineStr">
         <is>
           <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca  50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2101,53 +2096,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131038917</v>
+        <v>131040704</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gotvad, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>479105</v>
+        <v>479061</v>
       </c>
       <c r="R15" t="n">
-        <v>6792638</v>
+        <v>6792055</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2187,6 +2177,11 @@
       <c r="AB15" t="inlineStr">
         <is>
           <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca  50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2213,14 +2208,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131039391</v>
+        <v>131040880</v>
       </c>
       <c r="B16" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2244,17 +2239,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gotvad, Dlr</t>
+          <t>Tandbergsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479092</v>
+        <v>479089</v>
       </c>
       <c r="R16" t="n">
-        <v>6792603</v>
+        <v>6791921</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2298,7 +2293,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Miljöbilder. Rikligt till måttligt i en radie av ca 50 meter,  synfältet</t>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2325,14 +2320,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131040880</v>
+        <v>131041453</v>
       </c>
       <c r="B17" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2360,10 +2355,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479089</v>
+        <v>479034</v>
       </c>
       <c r="R17" t="n">
-        <v>6791921</v>
+        <v>6791697</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2437,14 +2432,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131039579</v>
+        <v>131041641</v>
       </c>
       <c r="B18" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2468,14 +2463,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gotvad, Dlr</t>
+          <t>Tandbergsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479079</v>
+        <v>479078</v>
       </c>
       <c r="R18" t="n">
-        <v>6792475</v>
+        <v>6791615</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2522,7 +2517,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2549,50 +2544,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131041965</v>
+        <v>131041815</v>
       </c>
       <c r="B19" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tandbergsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479096</v>
+        <v>479077</v>
       </c>
       <c r="R19" t="n">
-        <v>6792085</v>
+        <v>6791829</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2635,6 +2625,11 @@
       <c r="AB19" t="inlineStr">
         <is>
           <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2661,50 +2656,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131039828</v>
+        <v>131041972</v>
       </c>
       <c r="B20" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gotvad, Dlr</t>
+          <t>Tandbergsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479059</v>
+        <v>479096</v>
       </c>
       <c r="R20" t="n">
-        <v>6792254</v>
+        <v>6792085</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2749,11 +2739,16 @@
           <t>12:08</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="b">
         <v>0</v>
@@ -2773,14 +2768,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131040448</v>
+        <v>131042226</v>
       </c>
       <c r="B21" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2808,10 +2803,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479100</v>
+        <v>479114</v>
       </c>
       <c r="R21" t="n">
-        <v>6792209</v>
+        <v>6792438</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2843,7 +2838,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2853,12 +2848,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt till måttligt i en radie av ca  50 meter, synfältet</t>
+          <t>Rikligt till måttligt i en radie av ca 50 meter,synfältet</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2885,10 +2880,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131039488</v>
+        <v>131040483</v>
       </c>
       <c r="B22" t="n">
-        <v>79249</v>
+        <v>78730</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2896,21 +2891,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2920,10 +2915,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479104</v>
+        <v>479088</v>
       </c>
       <c r="R22" t="n">
-        <v>6792550</v>
+        <v>6792211</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2966,11 +2961,6 @@
       <c r="AB22" t="inlineStr">
         <is>
           <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2997,48 +2987,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131040704</v>
+        <v>131038653</v>
       </c>
       <c r="B23" t="n">
-        <v>79249</v>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gotvad, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479061</v>
+        <v>479094</v>
       </c>
       <c r="R23" t="n">
-        <v>6792055</v>
+        <v>6792753</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3078,11 +3073,6 @@
       <c r="AB23" t="inlineStr">
         <is>
           <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca  50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3109,48 +3099,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131038772</v>
+        <v>131041489</v>
       </c>
       <c r="B24" t="n">
-        <v>79249</v>
+        <v>57950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gotvad, Dlr</t>
+          <t>Tandbergsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479121</v>
+        <v>479034</v>
       </c>
       <c r="R24" t="n">
-        <v>6792727</v>
+        <v>6791697</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3190,11 +3185,6 @@
       <c r="AB24" t="inlineStr">
         <is>
           <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3221,10 +3211,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131038654</v>
+        <v>131038917</v>
       </c>
       <c r="B25" t="n">
-        <v>79249</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3232,34 +3222,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gotvad, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479094</v>
+        <v>479105</v>
       </c>
       <c r="R25" t="n">
-        <v>6792753</v>
+        <v>6792638</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3328,10 +3323,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131039672</v>
+        <v>131039548</v>
       </c>
       <c r="B26" t="n">
-        <v>79249</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3339,37 +3334,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gotvad, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479066</v>
+        <v>479052</v>
       </c>
       <c r="R26" t="n">
-        <v>6792326</v>
+        <v>6792508</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3409,11 +3409,6 @@
       <c r="AB26" t="inlineStr">
         <is>
           <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3440,10 +3435,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131039763</v>
+        <v>131039828</v>
       </c>
       <c r="B27" t="n">
-        <v>79249</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3451,24 +3446,29 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gotvad, Dlr</t>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AE27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG27" t="b">
         <v>0</v>
@@ -3544,6 +3544,663 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>131041965</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Tandbergsvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>479096</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6792085</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>131042212</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Gotvad, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>479114</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6792438</v>
+      </c>
+      <c r="S29" t="n">
+        <v>50</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131039519</v>
+      </c>
+      <c r="B30" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Gotvad, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>479079</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6792517</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131041349</v>
+      </c>
+      <c r="B31" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Tandbergsvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>479034</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6791697</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>131040374</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gotvad, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>479088</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6792211</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>131040796</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Tandbergsvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>479024</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6791902</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62829-2025 artfynd.xlsx
+++ b/artfynd/A 62829-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131039759</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131038578</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131038654</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131038772</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131039119</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131039391</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1436,6 +1471,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131039488</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1543,6 +1583,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131039523</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1655,6 +1700,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131039579</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1767,6 +1817,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131039672</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1874,6 +1929,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131039763</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1981,6 +2041,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131040375</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2093,6 +2158,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131040448</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2205,6 +2275,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131040704</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2317,6 +2392,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131040880</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2429,6 +2509,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131041453</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2541,6 +2626,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131041641</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2653,6 +2743,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131041815</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2765,6 +2860,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131041972</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2877,6 +2977,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131042226</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2984,6 +3089,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131040483</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3096,6 +3206,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131038653</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3208,6 +3323,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131041489</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3320,6 +3440,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131038917</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3432,6 +3557,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131039548</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3544,6 +3674,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131039828</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3656,6 +3791,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131041965</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3768,6 +3908,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131042212</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3880,6 +4025,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131039519</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3987,6 +4137,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131041349</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4094,6 +4249,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131040374</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4201,8 +4361,47 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131040796</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>